--- a/SBM-initDocIG/ig/all-profiles.xlsx
+++ b/SBM-initDocIG/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
